--- a/northwest_orders.xlsx
+++ b/northwest_orders.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,17 +423,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SalesOrderID</t>
+          <t>salesorderid</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OrderDate</t>
+          <t>orderdate</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>TotalDue</t>
+          <t>totaldue</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -445,15 +449,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75085</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75098</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C2" t="n">
-        <v>18.7187</v>
+        <v>41.1834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -462,21 +464,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AW00011927</t>
+          <t>10-4030-023381</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75098</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75104</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C3" t="n">
-        <v>41.1834</v>
+        <v>14.2987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -485,21 +485,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AW00023381</t>
+          <t>10-4030-017151</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75102</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75085</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C4" t="n">
-        <v>132.5779</v>
+        <v>18.7187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -508,21 +506,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AW00019893</t>
+          <t>10-4030-011927</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75104</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75102</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C5" t="n">
-        <v>14.2987</v>
+        <v>132.5779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -531,21 +527,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AW00017151</t>
+          <t>10-4030-019893</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>75107</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75119</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C6" t="n">
-        <v>62.9519</v>
+        <v>46.7194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -554,21 +548,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AW00014029</t>
+          <t>10-4030-011981</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>75119</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2014-06-30 00:00:00</t>
-        </is>
+        <v>75107</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>45837</v>
       </c>
       <c r="C7" t="n">
-        <v>46.7194</v>
+        <v>62.9519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -577,21 +569,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AW00011981</t>
+          <t>10-4030-014029</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75066</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75078</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C8" t="n">
-        <v>102.1904</v>
+        <v>81.72580000000001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -600,21 +590,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AW00029216</t>
+          <t>10-4030-022341</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75071</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75066</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C9" t="n">
-        <v>35.6584</v>
+        <v>102.1904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -623,7 +611,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AW00025858</t>
+          <t>10-4030-029216</t>
         </is>
       </c>
     </row>
@@ -631,10 +619,8 @@
       <c r="A10" t="n">
         <v>75074</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+      <c r="B10" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C10" t="n">
         <v>79.0959</v>
@@ -646,21 +632,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AW00024672</t>
+          <t>10-4030-024672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75076</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75080</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C11" t="n">
-        <v>43.6144</v>
+        <v>147.5065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -669,21 +653,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AW00023273</t>
+          <t>10-4030-018805</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>75078</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75081</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C12" t="n">
-        <v>81.72580000000001</v>
+        <v>85.0519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -692,21 +674,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AW00022341</t>
+          <t>10-4030-013929</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>75080</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75071</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C13" t="n">
-        <v>147.5065</v>
+        <v>35.6584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -715,21 +695,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AW00018805</t>
+          <t>10-4030-025858</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>75081</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2014-06-29 00:00:00</t>
-        </is>
+        <v>75076</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>45836</v>
       </c>
       <c r="C14" t="n">
-        <v>85.0519</v>
+        <v>43.6144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -738,7 +716,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AW00013929</t>
+          <t>10-4030-023273</t>
         </is>
       </c>
     </row>
@@ -746,10 +724,8 @@
       <c r="A15" t="n">
         <v>75043</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2014-06-28 00:00:00</t>
-        </is>
+      <c r="B15" s="1" t="n">
+        <v>45835</v>
       </c>
       <c r="C15" t="n">
         <v>77.339</v>
@@ -761,21 +737,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AW00020365</t>
+          <t>10-4030-020365</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>75044</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2014-06-28 00:00:00</t>
-        </is>
+        <v>75051</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>45835</v>
       </c>
       <c r="C16" t="n">
-        <v>16.5529</v>
+        <v>5.514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -784,21 +758,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AW00020473</t>
+          <t>10-4030-015300</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>75051</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2014-06-28 00:00:00</t>
-        </is>
+        <v>75044</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>45835</v>
       </c>
       <c r="C17" t="n">
-        <v>5.514</v>
+        <v>16.5529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -807,7 +779,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AW00015300</t>
+          <t>10-4030-020473</t>
         </is>
       </c>
     </row>
@@ -815,10 +787,8 @@
       <c r="A18" t="n">
         <v>75010</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2014-06-27 00:00:00</t>
-        </is>
+      <c r="B18" s="1" t="n">
+        <v>45834</v>
       </c>
       <c r="C18" t="n">
         <v>33.139</v>
@@ -830,21 +800,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AW00022277</t>
+          <t>10-4030-022277</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>75012</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2014-06-27 00:00:00</t>
-        </is>
+        <v>75029</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>45834</v>
       </c>
       <c r="C19" t="n">
-        <v>5.514</v>
+        <v>123.7158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -853,7 +821,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AW00017391</t>
+          <t>10-4030-012088</t>
         </is>
       </c>
     </row>
@@ -861,10 +829,8 @@
       <c r="A20" t="n">
         <v>75015</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2014-06-27 00:00:00</t>
-        </is>
+      <c r="B20" s="1" t="n">
+        <v>45834</v>
       </c>
       <c r="C20" t="n">
         <v>44.1779</v>
@@ -876,21 +842,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AW00014397</t>
+          <t>10-4030-014397</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>75029</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2014-06-27 00:00:00</t>
-        </is>
+        <v>75012</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>45834</v>
       </c>
       <c r="C21" t="n">
-        <v>123.7158</v>
+        <v>5.514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -899,21 +863,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AW00012088</t>
+          <t>10-4030-017391</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>74976</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2014-06-26 00:00:00</t>
-        </is>
+        <v>74982</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>45833</v>
       </c>
       <c r="C22" t="n">
-        <v>70.1344</v>
+        <v>88.3669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -922,21 +884,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AW00029262</t>
+          <t>10-4030-025877</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74978</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2014-06-26 00:00:00</t>
-        </is>
+        <v>74985</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>45833</v>
       </c>
       <c r="C23" t="n">
-        <v>2.5305</v>
+        <v>5.514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -945,21 +905,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AW00011219</t>
+          <t>10-4030-018668</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74979</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2014-06-26 00:00:00</t>
-        </is>
+        <v>74976</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>45833</v>
       </c>
       <c r="C24" t="n">
-        <v>93.88079999999999</v>
+        <v>70.1344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -968,21 +926,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AW00027735</t>
+          <t>10-4030-029262</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74982</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2014-06-26 00:00:00</t>
-        </is>
+        <v>74978</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>45833</v>
       </c>
       <c r="C25" t="n">
-        <v>88.3669</v>
+        <v>2.5305</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -991,21 +947,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AW00025877</t>
+          <t>10-4030-011219</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>74985</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2014-06-26 00:00:00</t>
-        </is>
+        <v>74979</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>45833</v>
       </c>
       <c r="C26" t="n">
-        <v>5.514</v>
+        <v>93.88079999999999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1014,21 +968,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AW00018668</t>
+          <t>10-4030-027735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74944</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+        <v>74960</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C27" t="n">
-        <v>140.2798</v>
+        <v>205.4969</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1037,21 +989,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AW00028634</t>
+          <t>10-4030-014575</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74950</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+        <v>74959</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C28" t="n">
-        <v>82.2783</v>
+        <v>60.7308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1060,21 +1010,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AW00021757</t>
+          <t>10-4030-014869</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74959</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+        <v>74967</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C29" t="n">
-        <v>60.7308</v>
+        <v>101.6269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1083,21 +1031,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AW00014869</t>
+          <t>10-4030-011786</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74960</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+        <v>74944</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C30" t="n">
-        <v>205.4969</v>
+        <v>140.2798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1106,21 +1052,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AW00014575</t>
+          <t>10-4030-028634</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>74967</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+        <v>74950</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C31" t="n">
-        <v>101.6269</v>
+        <v>82.2783</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1129,7 +1073,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AW00011786</t>
+          <t>10-4030-021757</t>
         </is>
       </c>
     </row>
@@ -1137,10 +1081,8 @@
       <c r="A32" t="n">
         <v>74968</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2014-06-25 00:00:00</t>
-        </is>
+      <c r="B32" s="1" t="n">
+        <v>45832</v>
       </c>
       <c r="C32" t="n">
         <v>79.5269</v>
@@ -1152,21 +1094,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AW00013295</t>
+          <t>10-4030-013295</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74927</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2014-06-24 00:00:00</t>
-        </is>
+        <v>74931</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>45831</v>
       </c>
       <c r="C33" t="n">
-        <v>47.4377</v>
+        <v>66.2779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1175,7 +1115,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AW00023291</t>
+          <t>10-4030-017589</t>
         </is>
       </c>
     </row>
@@ -1183,10 +1123,8 @@
       <c r="A34" t="n">
         <v>74928</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2014-06-24 00:00:00</t>
-        </is>
+      <c r="B34" s="1" t="n">
+        <v>45831</v>
       </c>
       <c r="C34" t="n">
         <v>38.6529</v>
@@ -1198,21 +1136,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AW00022263</t>
+          <t>10-4030-022263</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>74931</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2014-06-24 00:00:00</t>
-        </is>
+        <v>74932</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>45831</v>
       </c>
       <c r="C35" t="n">
-        <v>66.2779</v>
+        <v>109.3508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1221,21 +1157,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AW00017589</t>
+          <t>10-4030-016922</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>74932</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2014-06-24 00:00:00</t>
-        </is>
+        <v>74927</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>45831</v>
       </c>
       <c r="C36" t="n">
-        <v>109.3508</v>
+        <v>47.4377</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1244,21 +1178,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AW00016922</t>
+          <t>10-4030-023291</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>74884</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74898</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C37" t="n">
-        <v>5.514</v>
+        <v>87.27290000000001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1267,21 +1199,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AW00028277</t>
+          <t>10-4030-018797</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74885</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74888</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C38" t="n">
-        <v>8.0444</v>
+        <v>54.6754</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1290,21 +1220,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AW00028262</t>
+          <t>10-4030-025932</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>74886</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74908</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C39" t="n">
-        <v>26.2769</v>
+        <v>82.85290000000001</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1313,21 +1241,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AW00027741</t>
+          <t>10-4030-011013</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>74888</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74889</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C40" t="n">
-        <v>54.6754</v>
+        <v>27.614</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1336,21 +1262,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AW00025932</t>
+          <t>10-4030-025004</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>74889</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74910</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C41" t="n">
-        <v>27.614</v>
+        <v>41.2055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1359,21 +1283,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AW00025004</t>
+          <t>10-4030-012776</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>74890</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74885</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C42" t="n">
-        <v>79.0959</v>
+        <v>8.0444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1382,7 +1304,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AW00025187</t>
+          <t>10-4030-028262</t>
         </is>
       </c>
     </row>
@@ -1390,10 +1312,8 @@
       <c r="A43" t="n">
         <v>74891</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+      <c r="B43" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C43" t="n">
         <v>35.6694</v>
@@ -1405,21 +1325,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AW00023037</t>
+          <t>10-4030-023037</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>74896</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74890</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C44" t="n">
-        <v>77.339</v>
+        <v>79.0959</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1428,21 +1346,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AW00018870</t>
+          <t>10-4030-025187</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>74898</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74884</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C45" t="n">
-        <v>87.27290000000001</v>
+        <v>5.514</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1451,21 +1367,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AW00018797</t>
+          <t>10-4030-028277</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>74908</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74886</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C46" t="n">
-        <v>82.85290000000001</v>
+        <v>26.2769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1474,21 +1388,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AW00011013</t>
+          <t>10-4030-027741</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>74910</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2014-06-23 00:00:00</t>
-        </is>
+        <v>74896</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>45830</v>
       </c>
       <c r="C47" t="n">
-        <v>41.2055</v>
+        <v>77.339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1497,21 +1409,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AW00012776</t>
+          <t>10-4030-018870</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>74843</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2014-06-22 00:00:00</t>
-        </is>
+        <v>74857</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>45829</v>
       </c>
       <c r="C48" t="n">
-        <v>6.9394</v>
+        <v>92.7869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1520,21 +1430,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AW00011137</t>
+          <t>10-4030-027538</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>74857</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2014-06-22 00:00:00</t>
-        </is>
+        <v>74860</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>45829</v>
       </c>
       <c r="C49" t="n">
-        <v>92.7869</v>
+        <v>16.5529</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1543,21 +1451,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AW00027538</t>
+          <t>10-4030-021617</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>74860</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2014-06-22 00:00:00</t>
-        </is>
+        <v>74864</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>45829</v>
       </c>
       <c r="C50" t="n">
-        <v>16.5529</v>
+        <v>142.5119</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1566,21 +1472,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AW00021617</t>
+          <t>10-4030-018813</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>74864</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2014-06-22 00:00:00</t>
-        </is>
+        <v>74843</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>45829</v>
       </c>
       <c r="C51" t="n">
-        <v>142.5119</v>
+        <v>6.9394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1589,7 +1493,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AW00018813</t>
+          <t>10-4030-011137</t>
         </is>
       </c>
     </row>
